--- a/fFacial.xlsx
+++ b/fFacial.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/BI_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCDAFB06-EB5A-47D1-8CDB-3586ACDA1100}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B5B624-27A4-4C2A-B0BD-4F7676135491}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{87DA37B0-848D-436B-BEE1-46F60B206BED}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>fac-16</t>
   </si>
@@ -213,6 +213,24 @@
   </si>
   <si>
     <t>2025.09.20-CAMBR2-24</t>
+  </si>
+  <si>
+    <t>2025.10.01-CAMBR2-26</t>
+  </si>
+  <si>
+    <t>2025.10.15-CAMBR2-28</t>
+  </si>
+  <si>
+    <t>2026.03.07-CAMCA4-FINAL - TR</t>
+  </si>
+  <si>
+    <t>2026.03.10-CAMLI5-3° Fase</t>
+  </si>
+  <si>
+    <t>2026.03.14-CAMBR2-6</t>
+  </si>
+  <si>
+    <t>2026.04.01-CAMBR2-9</t>
   </si>
 </sst>
 </file>
@@ -606,10 +624,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6262C255-C934-4E6E-8069-0C0204B67DBD}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
@@ -1235,6 +1253,138 @@
         <v>-30800</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="5">
+        <v>-27000</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="5">
+        <v>-3800</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="5">
+        <v>-3800</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="5">
+        <v>-27000</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="5">
+        <v>-27000</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5">
+        <v>-3800</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5">
+        <v>-27000</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5">
+        <v>-3800</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="5">
+        <v>-27000</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="5">
+        <v>-3800</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="5">
+        <v>-27000</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="5">
+        <v>-3800</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>0</v>
       </c>
     </row>

--- a/fFacial.xlsx
+++ b/fFacial.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B5B624-27A4-4C2A-B0BD-4F7676135491}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F02CE2-91BA-475A-A387-1008604376A0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{87DA37B0-848D-436B-BEE1-46F60B206BED}"/>
+    <workbookView xWindow="-28920" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{87DA37B0-848D-436B-BEE1-46F60B206BED}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="72">
   <si>
     <t>fac-16</t>
   </si>
@@ -231,6 +231,30 @@
   </si>
   <si>
     <t>2026.04.01-CAMBR2-9</t>
+  </si>
+  <si>
+    <t>2026.01.21-CAMCA4-3</t>
+  </si>
+  <si>
+    <t>2026.01.24-CAMCA4-4</t>
+  </si>
+  <si>
+    <t>2026.01.29-CAMBR2-1</t>
+  </si>
+  <si>
+    <t>2026.02.01-CAMCA4-5</t>
+  </si>
+  <si>
+    <t>2026.02.15-CAMCA4-Quartas</t>
+  </si>
+  <si>
+    <t>2026.02.25-CAMLI5-2° FASE</t>
+  </si>
+  <si>
+    <t>2026.02.28-CAMCA4-SEMIS - TR</t>
+  </si>
+  <si>
+    <t>2026.04.12-CAMBR2-11</t>
   </si>
 </sst>
 </file>
@@ -624,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6262C255-C934-4E6E-8069-0C0204B67DBD}">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.54296875" style="3" bestFit="1" customWidth="1"/>
@@ -1388,6 +1412,94 @@
         <v>0</v>
       </c>
     </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B69" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>71</v>
+      </c>
+      <c r="B75" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{6262C255-C934-4E6E-8069-0C0204B67DBD}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C48">

--- a/fFacial.xlsx
+++ b/fFacial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/dash-ticket/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F02CE2-91BA-475A-A387-1008604376A0}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F71D2F10-F06A-437C-B3E1-779C1A7E4D3A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{87DA37B0-848D-436B-BEE1-46F60B206BED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{87DA37B0-848D-436B-BEE1-46F60B206BED}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="71">
   <si>
     <t>fac-16</t>
   </si>
@@ -233,28 +233,25 @@
     <t>2026.04.01-CAMBR2-9</t>
   </si>
   <si>
-    <t>2026.01.21-CAMCA4-3</t>
-  </si>
-  <si>
-    <t>2026.01.24-CAMCA4-4</t>
-  </si>
-  <si>
-    <t>2026.01.29-CAMBR2-1</t>
-  </si>
-  <si>
-    <t>2026.02.01-CAMCA4-5</t>
-  </si>
-  <si>
-    <t>2026.02.15-CAMCA4-Quartas</t>
-  </si>
-  <si>
-    <t>2026.02.25-CAMLI5-2° FASE</t>
-  </si>
-  <si>
-    <t>2026.02.28-CAMCA4-SEMIS - TR</t>
+    <t>2026.04.09-CAMSU6-FG</t>
   </si>
   <si>
     <t>2026.04.12-CAMBR2-11</t>
+  </si>
+  <si>
+    <t>2026.04.21-CAMCO3-5° Fase</t>
+  </si>
+  <si>
+    <t>2026.04.28-CAMSU6-FG</t>
+  </si>
+  <si>
+    <t>2026.05.02-CAMBR2-14</t>
+  </si>
+  <si>
+    <t>2026.05.06-CAMSU6-FG</t>
+  </si>
+  <si>
+    <t>2026.05.17-CAMBR2-16</t>
   </si>
 </sst>
 </file>
@@ -648,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6262C255-C934-4E6E-8069-0C0204B67DBD}">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.54296875" style="3" bestFit="1" customWidth="1"/>
@@ -1293,7 +1290,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57" s="5">
         <v>-3800</v>
@@ -1304,7 +1301,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" s="5">
         <v>-3800</v>
@@ -1413,7 +1410,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B68" s="5">
@@ -1424,7 +1421,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B69" s="5">
@@ -1435,7 +1432,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B70" s="5">
@@ -1446,7 +1443,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B71" s="5">
@@ -1457,7 +1454,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B72" s="5">
@@ -1468,7 +1465,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B73" s="5">
@@ -1479,30 +1476,19 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B74" s="5">
         <v>-30800</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>71</v>
-      </c>
-      <c r="B75" s="5">
-        <v>-30800</v>
-      </c>
-      <c r="C75" s="3" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{6262C255-C934-4E6E-8069-0C0204B67DBD}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C48">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C67">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/fFacial.xlsx
+++ b/fFacial.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B5B624-27A4-4C2A-B0BD-4F7676135491}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{D9D2D1F5-F5B2-413B-9EF5-9E3621390E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F71D2F10-F06A-437C-B3E1-779C1A7E4D3A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{87DA37B0-848D-436B-BEE1-46F60B206BED}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="71">
   <si>
     <t>fac-16</t>
   </si>
@@ -231,6 +231,27 @@
   </si>
   <si>
     <t>2026.04.01-CAMBR2-9</t>
+  </si>
+  <si>
+    <t>2026.04.09-CAMSU6-FG</t>
+  </si>
+  <si>
+    <t>2026.04.12-CAMBR2-11</t>
+  </si>
+  <si>
+    <t>2026.04.21-CAMCO3-5° Fase</t>
+  </si>
+  <si>
+    <t>2026.04.28-CAMSU6-FG</t>
+  </si>
+  <si>
+    <t>2026.05.02-CAMBR2-14</t>
+  </si>
+  <si>
+    <t>2026.05.06-CAMSU6-FG</t>
+  </si>
+  <si>
+    <t>2026.05.17-CAMBR2-16</t>
   </si>
 </sst>
 </file>
@@ -624,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6262C255-C934-4E6E-8069-0C0204B67DBD}">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.54296875" style="3" bestFit="1" customWidth="1"/>
@@ -1269,7 +1290,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57" s="5">
         <v>-3800</v>
@@ -1280,7 +1301,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" s="5">
         <v>-3800</v>
@@ -1388,9 +1409,86 @@
         <v>0</v>
       </c>
     </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B69" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" s="5">
+        <v>-30800</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{6262C255-C934-4E6E-8069-0C0204B67DBD}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C48">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C67">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
